--- a/output/leads_robotics_2026-07-31.xlsx
+++ b/output/leads_robotics_2026-07-31.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Robotics &amp; Automatio" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Robotics &amp; Automatio'!$A$1:$I$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Robotics &amp; Automatio'!$A$1:$I$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -58,12 +58,6 @@
         <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -83,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -95,9 +89,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -465,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -529,20 +520,20 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>DHL Supply Chain (Deutsche Post DHL Group)</t>
+          <t>ZF Friedrichshafen AG</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Warehouse &amp; Logistics Operator (3PL)</t>
+          <t>Automotive Tier 1 Supplier</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -562,32 +553,32 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=DHL%20Supply%20Chain%20%28Deutsche%20Post%20DHL%20Group%29</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=ZF%20Friedrichshafen%20AG</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>DHL aggressively automates warehouses globally and Chinese robotics firms provide affordable AMRs and sortation systems that fit their volume needs.</t>
+          <t>ZF's global powertrain and chassis plants need high-volume robotic assembly and material handling, where Chinese exporters offer competitive pricing.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Samsung Electronics Co., Ltd.</t>
+          <t>Continental AG</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Electronics Manufacturer (Semiconductor/PCB)</t>
+          <t>Automotive Tier 1 Supplier</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -597,7 +588,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -607,32 +598,32 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Samsung%20Electronics%20Co.%2C%20Ltd.</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Continental%20AG</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Samsung's massive electronics assembly and semiconductor fabs need high-volume, cost-effective robotic handling and inspection systems, a sweet spot for Chinese exporters.</t>
+          <t>Continental's electronics and tire manufacturing operations require precision automation, and Chinese robotics are increasingly viable for cost-sensitive lines.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Magna International Inc.</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Automotive Tier 1 Supplier</t>
+          <t>Automotive Manufacturer</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -642,7 +633,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -652,32 +643,32 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Magna%20International%20Inc.</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=General%20Motors%20Company</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Magna's global manufacturing footprint and cost pressures drive them to source competitive automation and robotics from China for assembly and welding lines.</t>
+          <t>GM is investing heavily in EV and battery manufacturing, requiring automation for assembly and material handling, and Chinese suppliers offer cost-competitive robotics.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Bosch GmbH (Robert Bosch GmbH)</t>
+          <t>PepsiCo, Inc.</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Electronics Manufacturer / Tier 1 Supplier</t>
+          <t>Food &amp; Beverage Processing Plant</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -687,7 +678,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -697,32 +688,32 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Bosch%20GmbH%20%28Robert%20Bosch%20GmbH%29</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=PepsiCo%2C%20Inc.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Bosch's vast electronics and automotive components operations need cost-efficient robotics for PCB assembly and material handling, where Chinese vendors excel.</t>
+          <t>High-volume beverage and snack production requires fast, reliable automation, and Chinese robotics are increasingly competitive in speed and price.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>LG Electronics Inc.</t>
+          <t>XPO Logistics, Inc.</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Electronics Manufacturer</t>
+          <t>Warehouse &amp; Logistics Operator (3PL)</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -732,7 +723,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -742,32 +733,32 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=LG%20Electronics%20Inc.</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=XPO%20Logistics%2C%20Inc.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>LG's appliance and component plants require affordable automation for assembly and packaging, making Chinese robotics a strong fit.</t>
+          <t>US-based 3PL with heavy warehouse automation needs, but may prefer domestic or established suppliers; still open to Chinese cost advantages.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ThyssenKrupp AG</t>
+          <t>Kia Corporation</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Metal Fabrication &amp; Welding Shop</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>80</v>
+          <t>Automotive Manufacturer</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>68</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -777,7 +768,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -787,28 +778,28 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=ThyssenKrupp%20AG</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Kia%20Corporation</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>ThyssenKrupp's steel and industrial operations require heavy-duty welding and material handling robots, and Chinese manufacturers offer cost-effective solutions for high-volume fabrication.</t>
+          <t>Kia's manufacturing expansion and cost optimization drive interest in Chinese welding and assembly robots, especially in emerging markets.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>ArcelorMittal S.A.</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Automotive Manufacturer</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>75</v>
+          <t>Metal Fabrication &amp; Welding Shop</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>65</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -832,28 +823,28 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Ford%20Motor%20Company</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=ArcelorMittal%20S.A.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Ford is automating EV and legacy plants, and Chinese robotics offer cost-effective, high-volume solutions for assembly and welding.</t>
+          <t>Steel giant uses heavy-duty robotic welding and material handling, but their needs are highly specialized and often met by European suppliers; still, Chinese heavy-duty robots are gaining traction.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>General Motors LLC</t>
+          <t>C.H. Robinson Worldwide, Inc.</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Automotive Manufacturer</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>75</v>
+          <t>Warehouse &amp; Logistics Operator (3PL)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>60</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -877,647 +868,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=General%20Motors%20LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=C.H.%20Robinson%20Worldwide%2C%20Inc.</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>GM's aggressive EV ramp-up requires flexible automation, and Chinese suppliers provide competitive pricing on robotic cells and AGVs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Linamar Corporation</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Automotive Tier 1 Supplier</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>DeepSeek Knowledge Base</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Linamar%20Corporation</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Linamar's metal cutting and machining operations need cost-effective robotic handling and CNC automation, which Chinese suppliers offer at scale.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Magna International (again? no, use another) – instead: ABC Technologies Inc.</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Automotive Tier 1 Supplier</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>DeepSeek Knowledge Base</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Magna%20International%20%28again%3F%20no%2C%20use%20another%29%20%E2%80%93%20instead%3A%20ABC%20Technologies%20Inc.</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>As a major automotive plastics and systems supplier, they need cost-effective robotic welding, assembly, and material handling automation to stay competitive against Chinese EV supply chains.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Siemens AG</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Electronics Manufacturer / Automation Supplier</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>DeepSeek Knowledge Base</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Siemens%20AG</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Siemens integrates automation but may source specific robotic components from China for cost competitiveness in its factory solutions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Volkswagen AG</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Automotive Manufacturer</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>DeepSeek Knowledge Base</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Volkswagen%20AG</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>VW's global plant modernization and EV transition create demand for affordable robotic welding and assembly systems from China.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Kuehne + Nagel International AG</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Warehouse &amp; Logistics Operator (3PL)</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>DeepSeek Knowledge Base</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Kuehne%20%2B%20Nagel%20International%20AG</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Kuehne+Nagel's contract logistics operations increasingly adopt automation, and Chinese suppliers offer cost-effective solutions for palletizing and picking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Hyundai Motor Company</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Automotive Manufacturer</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>DeepSeek Knowledge Base</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hyundai%20Motor%20Company</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Hyundai is expanding robotics use (including via Boston Dynamics) but may source from China for cost-effective welding and logistics robots in its plants.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Voestalpine AG</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Metal Fabrication &amp; Welding Shop</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>DeepSeek Knowledge Base</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Voestalpine%20AG</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Voestalpine's precision metal processing and welding operations could benefit from Chinese robotic cells, though they may prioritize European suppliers for technical support.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Toyota Motor Corporation</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Automotive Manufacturer</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>DeepSeek Knowledge Base</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Toyota%20Motor%20Corporation</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>Toyota's conservative supply chain and high quality standards may limit Chinese robotics adoption, but they still evaluate cost-effective automation for non-critical tasks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Cargill, Incorporated</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Food &amp; Beverage Processing Plant</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>DeepSeek Knowledge Base</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Cargill%2C%20Incorporated</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Cargill's food processing plants need hygienic, high-speed packaging and palletizing robots, and Chinese vendors provide competitive pricing for standard models.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Honda Motor Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Automotive Manufacturer</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>DeepSeek Knowledge Base</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Honda%20Motor%20Co.%2C%20Ltd.</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Honda has strong domestic automation partnerships, but may consider Chinese robots for peripheral operations like painting or logistics.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Nestlé S.A.</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Food &amp; Beverage Processing Plant</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>DeepSeek Knowledge Base</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Nestl%C3%A9%20S.A.</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Nestlé has strict global quality standards and often prefers established Western automation partners, but may consider Chinese robots for secondary packaging in cost-sensitive markets.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Berry Global Group, Inc.</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Plastics &amp; Injection Molding Company</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>DeepSeek Knowledge Base</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Berry%20Global%20Group%2C%20Inc.</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>They may source injection molding machines and automation for packaging production, but their focus is high-volume consumer goods, not precision robotics, so China is a secondary option.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Pfizer Inc.</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Pharmaceutical Manufacturer</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>DeepSeek Knowledge Base</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Pfizer%20Inc.</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Pharmaceutical manufacturing demands high regulatory compliance and validation, making Chinese robotics less attractive unless they meet stringent GMP standards.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Bayer AG</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Pharmaceutical Manufacturer</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>DeepSeek Knowledge Base</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Bayer%20AG</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Bayer's pharma and crop science operations require specialized, validated automation, and they typically source from established Western vendors with proven track records.</t>
+          <t>Primarily a freight broker, but their warehouse operations could adopt Chinese robotics for sorting and loading, though less automation-intensive than peers.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I23"/>
+  <autoFilter ref="A1:I9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>